--- a/Pruebas calificadas/COLEGIO-MARIA-CURREA-MANRIQUE-(IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-MARIA-CURREA-MANRIQUE-(IED)-901_CALIFICADO.xlsx
@@ -938,9 +938,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1950,9 +1950,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -3717,9 +3717,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -4729,9 +4729,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -4982,9 +4982,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -5741,9 +5741,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -6753,9 +6753,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -7006,9 +7006,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB26" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -7512,9 +7512,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB28" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -8018,9 +8018,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB30" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -8271,9 +8271,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -8524,9 +8524,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -8777,9 +8777,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB33" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -9283,9 +9283,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB35" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -9789,9 +9789,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB37" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -10295,9 +10295,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB39" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-MARIA-CURREA-MANRIQUE-(IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-MARIA-CURREA-MANRIQUE-(IED)-901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11176,11 +11012,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11429,11 +11261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11682,11 +11510,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11931,11 +11755,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12184,11 +12004,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12437,11 +12253,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12690,11 +12502,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12943,11 +12751,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13196,11 +13000,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13449,11 +13249,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13702,11 +13498,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13955,11 +13747,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14208,11 +13996,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14461,11 +14245,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14714,11 +14494,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14967,11 +14743,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15220,11 +14992,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15473,11 +15241,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15726,11 +15490,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15971,11 +15731,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16224,11 +15980,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16477,11 +16229,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16730,11 +16478,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16983,11 +16727,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17232,11 +16972,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17485,11 +17221,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17738,11 +17470,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17991,11 +17719,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18244,11 +17968,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18497,11 +18217,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18750,11 +18466,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18971,11 +18683,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19188,11 +18896,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19401,11 +19105,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19654,11 +19354,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
